--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/135.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/135.xlsx
@@ -426,13 +426,13 @@
         <v>-5.133164841604869</v>
       </c>
       <c r="E2">
-        <v>-16.72646424091899</v>
+        <v>-19.19908803316513</v>
       </c>
       <c r="F2">
-        <v>-1.361432742524732</v>
+        <v>-0.7782405534014069</v>
       </c>
       <c r="G2">
-        <v>-6.933836155760118</v>
+        <v>-9.970741932391766</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.245100895038108</v>
       </c>
       <c r="E3">
-        <v>-16.30022162494701</v>
+        <v>-18.77344317576217</v>
       </c>
       <c r="F3">
-        <v>-1.360392313066815</v>
+        <v>-0.5946561128581749</v>
       </c>
       <c r="G3">
-        <v>-7.53214774052706</v>
+        <v>-9.895443574101042</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.29935716397299</v>
       </c>
       <c r="E4">
-        <v>-17.41700671387463</v>
+        <v>-18.9224707268806</v>
       </c>
       <c r="F4">
-        <v>-1.295046550496976</v>
+        <v>-0.06048090806070525</v>
       </c>
       <c r="G4">
-        <v>-6.944042567657691</v>
+        <v>-9.587903825139367</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.240450827753239</v>
       </c>
       <c r="E5">
-        <v>-18.47441445161368</v>
+        <v>-20.79164365828661</v>
       </c>
       <c r="F5">
-        <v>-0.6481785874878565</v>
+        <v>-0.6945282287766973</v>
       </c>
       <c r="G5">
-        <v>-7.164786433670755</v>
+        <v>-10.57111267648414</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.047222531731709</v>
       </c>
       <c r="E6">
-        <v>-19.84759721038158</v>
+        <v>-21.04920967442088</v>
       </c>
       <c r="F6">
-        <v>-0.8680811400720273</v>
+        <v>-0.5665380097375484</v>
       </c>
       <c r="G6">
-        <v>-6.94622421716807</v>
+        <v>-10.33250179619563</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.694373927791857</v>
       </c>
       <c r="E7">
-        <v>-19.39248104413671</v>
+        <v>-21.02919834778099</v>
       </c>
       <c r="F7">
-        <v>-0.7710155329141896</v>
+        <v>-0.5249075775424564</v>
       </c>
       <c r="G7">
-        <v>-6.389668543287955</v>
+        <v>-9.2028344101935</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.16703082480388</v>
       </c>
       <c r="E8">
-        <v>-20.11907469866741</v>
+        <v>-22.79917505604898</v>
       </c>
       <c r="F8">
-        <v>-0.7396419459005611</v>
+        <v>-0.379877012660319</v>
       </c>
       <c r="G8">
-        <v>-6.566643686726315</v>
+        <v>-10.56450482758775</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.464623087748322</v>
       </c>
       <c r="E9">
-        <v>-21.01469364553442</v>
+        <v>-23.316951717138</v>
       </c>
       <c r="F9">
-        <v>-0.3313247424474344</v>
+        <v>0.1949105607942019</v>
       </c>
       <c r="G9">
-        <v>-6.32882733736723</v>
+        <v>-9.229914672704739</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.608251647294761</v>
       </c>
       <c r="E10">
-        <v>-22.02002846065926</v>
+        <v>-23.93826287946438</v>
       </c>
       <c r="F10">
-        <v>-0.6575101462803929</v>
+        <v>0.4779239406954586</v>
       </c>
       <c r="G10">
-        <v>-6.459911698540211</v>
+        <v>-8.686558143889698</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.637933505184242</v>
       </c>
       <c r="E11">
-        <v>-22.60509824550225</v>
+        <v>-24.92347315609913</v>
       </c>
       <c r="F11">
-        <v>-0.6797708634958241</v>
+        <v>0.1974859550495056</v>
       </c>
       <c r="G11">
-        <v>-5.093371468657694</v>
+        <v>-8.183868356479065</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.6092241570172017</v>
       </c>
       <c r="E12">
-        <v>-22.22855110329046</v>
+        <v>-25.54848408168978</v>
       </c>
       <c r="F12">
-        <v>-0.6976710547029186</v>
+        <v>0.5247515499757147</v>
       </c>
       <c r="G12">
-        <v>-4.65623048292463</v>
+        <v>-7.205767676901393</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.4207528899841543</v>
       </c>
       <c r="E13">
-        <v>-24.68836837104291</v>
+        <v>-26.14101226322341</v>
       </c>
       <c r="F13">
-        <v>-0.6463387834862389</v>
+        <v>0.4502746935248167</v>
       </c>
       <c r="G13">
-        <v>-4.511076303209745</v>
+        <v>-6.849811199427876</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.398964044663011</v>
       </c>
       <c r="E14">
-        <v>-26.30173686270365</v>
+        <v>-26.83680323755394</v>
       </c>
       <c r="F14">
-        <v>-0.1474743959679037</v>
+        <v>0.324486275042309</v>
       </c>
       <c r="G14">
-        <v>-4.100154838147709</v>
+        <v>-7.108176104949217</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.285084267547806</v>
       </c>
       <c r="E15">
-        <v>-26.28920657512442</v>
+        <v>-28.96322066343968</v>
       </c>
       <c r="F15">
-        <v>0.1653502700253016</v>
+        <v>0.8459891153117517</v>
       </c>
       <c r="G15">
-        <v>-3.579425888093588</v>
+        <v>-6.214553926442667</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.053223385146455</v>
       </c>
       <c r="E16">
-        <v>-27.76600534766183</v>
+        <v>-28.89423841888084</v>
       </c>
       <c r="F16">
-        <v>0.1402374838420317</v>
+        <v>1.116550476414126</v>
       </c>
       <c r="G16">
-        <v>-2.981971734621316</v>
+        <v>-5.85001320438582</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.687145399711906</v>
       </c>
       <c r="E17">
-        <v>-28.54342206598063</v>
+        <v>-29.65175022969892</v>
       </c>
       <c r="F17">
-        <v>0.101605741645074</v>
+        <v>1.099255821778478</v>
       </c>
       <c r="G17">
-        <v>-2.16278386201974</v>
+        <v>-5.128850585202064</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.179401414058074</v>
       </c>
       <c r="E18">
-        <v>-28.98967148011848</v>
+        <v>-31.13793652885423</v>
       </c>
       <c r="F18">
-        <v>0.1703502956685994</v>
+        <v>1.079090045724727</v>
       </c>
       <c r="G18">
-        <v>-1.349564903025469</v>
+        <v>-3.352504544104244</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.526669289720455</v>
       </c>
       <c r="E19">
-        <v>-31.04029810077485</v>
+        <v>-30.77584880414892</v>
       </c>
       <c r="F19">
-        <v>0.304984849645603</v>
+        <v>1.424502685344065</v>
       </c>
       <c r="G19">
-        <v>-2.708335282527317</v>
+        <v>-4.136047772884488</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>4.732430962137762</v>
       </c>
       <c r="E20">
-        <v>-30.08226319666012</v>
+        <v>-31.33785733510786</v>
       </c>
       <c r="F20">
-        <v>0.2160041083390885</v>
+        <v>1.275086743431507</v>
       </c>
       <c r="G20">
-        <v>-1.43554639177142</v>
+        <v>-3.286267148954506</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.806855085650007</v>
       </c>
       <c r="E21">
-        <v>-30.28853745194651</v>
+        <v>-31.80190138785886</v>
       </c>
       <c r="F21">
-        <v>0.5855446052997676</v>
+        <v>1.886607440995769</v>
       </c>
       <c r="G21">
-        <v>-0.7875633817332529</v>
+        <v>-4.337709654409192</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.768002306334412</v>
       </c>
       <c r="E22">
-        <v>-31.51685432720904</v>
+        <v>-33.19435959624041</v>
       </c>
       <c r="F22">
-        <v>0.3634236848108998</v>
+        <v>1.418800204143193</v>
       </c>
       <c r="G22">
-        <v>-1.012316318394374</v>
+        <v>-3.202556694448495</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.638546924160554</v>
       </c>
       <c r="E23">
-        <v>-31.59173264492587</v>
+        <v>-33.50110257586098</v>
       </c>
       <c r="F23">
-        <v>0.6669590387491114</v>
+        <v>1.476933371736857</v>
       </c>
       <c r="G23">
-        <v>-0.4343811414216456</v>
+        <v>-3.442905611145122</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.445723291794263</v>
       </c>
       <c r="E24">
-        <v>-32.59473303169976</v>
+        <v>-33.54638052322667</v>
       </c>
       <c r="F24">
-        <v>0.6947308842953677</v>
+        <v>1.142922381049651</v>
       </c>
       <c r="G24">
-        <v>-0.3970812248306771</v>
+        <v>-2.722888440717953</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.216178744942112</v>
       </c>
       <c r="E25">
-        <v>-32.05478269763219</v>
+        <v>-33.82368842179737</v>
       </c>
       <c r="F25">
-        <v>0.4494960281661852</v>
+        <v>1.707361988908401</v>
       </c>
       <c r="G25">
-        <v>-0.5152544584005014</v>
+        <v>-2.422929841041209</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.972455800196301</v>
       </c>
       <c r="E26">
-        <v>-33.12709590756748</v>
+        <v>-33.79525639774021</v>
       </c>
       <c r="F26">
-        <v>0.6478063560289841</v>
+        <v>1.130056178549369</v>
       </c>
       <c r="G26">
-        <v>-0.4395389713718301</v>
+        <v>-3.5089609262902</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.734775725833569</v>
       </c>
       <c r="E27">
-        <v>-32.4429114121186</v>
+        <v>-33.89820446159359</v>
       </c>
       <c r="F27">
-        <v>0.6839380854042929</v>
+        <v>1.59307710854857</v>
       </c>
       <c r="G27">
-        <v>-1.294907796172102</v>
+        <v>-3.166736591713581</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.510998600120368</v>
       </c>
       <c r="E28">
-        <v>-31.35230316719232</v>
+        <v>-34.45790120657161</v>
       </c>
       <c r="F28">
-        <v>0.2888093193711371</v>
+        <v>1.304984179733347</v>
       </c>
       <c r="G28">
-        <v>-0.4001633427277386</v>
+        <v>-2.952401941864546</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.303305948067512</v>
       </c>
       <c r="E29">
-        <v>-31.00060602609762</v>
+        <v>-33.65676207716363</v>
       </c>
       <c r="F29">
-        <v>0.02172213115610368</v>
+        <v>1.483318427677635</v>
       </c>
       <c r="G29">
-        <v>-1.191890240081061</v>
+        <v>-2.71318192119681</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.104441899604609</v>
       </c>
       <c r="E30">
-        <v>-30.69923155241315</v>
+        <v>-33.53137542460225</v>
       </c>
       <c r="F30">
-        <v>0.1182874044026505</v>
+        <v>1.484874101660093</v>
       </c>
       <c r="G30">
-        <v>-1.059792851973062</v>
+        <v>-3.38418315436953</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.901503177946418</v>
       </c>
       <c r="E31">
-        <v>-30.09179789868327</v>
+        <v>-33.27525625591343</v>
       </c>
       <c r="F31">
-        <v>0.5280849004045799</v>
+        <v>1.50679933007739</v>
       </c>
       <c r="G31">
-        <v>-1.460772748780667</v>
+        <v>-3.795581337989221</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.684692993951168</v>
       </c>
       <c r="E32">
-        <v>-30.59295053169013</v>
+        <v>-33.54559483298634</v>
       </c>
       <c r="F32">
-        <v>0.2622154122716617</v>
+        <v>0.8445610099093254</v>
       </c>
       <c r="G32">
-        <v>-2.226823054931402</v>
+        <v>-4.458650504049847</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.441846379127929</v>
       </c>
       <c r="E33">
-        <v>-30.53015871109977</v>
+        <v>-31.72106359834793</v>
       </c>
       <c r="F33">
-        <v>0.3141921533277195</v>
+        <v>1.007640043763659</v>
       </c>
       <c r="G33">
-        <v>-1.682681926823554</v>
+        <v>-3.911334562769838</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.166823750622195</v>
       </c>
       <c r="E34">
-        <v>-29.85206274895421</v>
+        <v>-31.4863075057903</v>
       </c>
       <c r="F34">
-        <v>0.6718389511190033</v>
+        <v>0.7595887384649577</v>
       </c>
       <c r="G34">
-        <v>-1.977615118371684</v>
+        <v>-5.154507313131415</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.856230636273156</v>
       </c>
       <c r="E35">
-        <v>-29.71976790929413</v>
+        <v>-30.35920655307321</v>
       </c>
       <c r="F35">
-        <v>0.4671725601745239</v>
+        <v>1.404737839113269</v>
       </c>
       <c r="G35">
-        <v>-2.088111196835939</v>
+        <v>-5.140967181875796</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.509420731091253</v>
       </c>
       <c r="E36">
-        <v>-28.38174648695878</v>
+        <v>-31.19567230821502</v>
       </c>
       <c r="F36">
-        <v>0.6990947237733154</v>
+        <v>1.401760686667607</v>
       </c>
       <c r="G36">
-        <v>-3.561393346541177</v>
+        <v>-4.599782370934517</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.132252275547167</v>
       </c>
       <c r="E37">
-        <v>-27.66603928394251</v>
+        <v>-30.67035347366624</v>
       </c>
       <c r="F37">
-        <v>0.6707629018627668</v>
+        <v>1.311955719795307</v>
       </c>
       <c r="G37">
-        <v>-2.190906946375848</v>
+        <v>-5.365898887996037</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.7324151674045775</v>
       </c>
       <c r="E38">
-        <v>-27.13293826681154</v>
+        <v>-29.26277016209906</v>
       </c>
       <c r="F38">
-        <v>0.7018457319180126</v>
+        <v>1.66251252098603</v>
       </c>
       <c r="G38">
-        <v>-3.437790818286948</v>
+        <v>-5.326688786628909</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.3211739503683589</v>
       </c>
       <c r="E39">
-        <v>-25.16393965438044</v>
+        <v>-29.7988645005491</v>
       </c>
       <c r="F39">
-        <v>1.291215056764013</v>
+        <v>1.812690560909164</v>
       </c>
       <c r="G39">
-        <v>-3.410084862668788</v>
+        <v>-4.92904591972489</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.08814163615968308</v>
       </c>
       <c r="E40">
-        <v>-25.89229941377414</v>
+        <v>-29.0635399481316</v>
       </c>
       <c r="F40">
-        <v>1.438999114893056</v>
+        <v>1.486279012775241</v>
       </c>
       <c r="G40">
-        <v>-4.195601176590437</v>
+        <v>-5.830236005334214</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.4814127271793253</v>
       </c>
       <c r="E41">
-        <v>-26.08236852482408</v>
+        <v>-27.84327469965471</v>
       </c>
       <c r="F41">
-        <v>1.365145190729063</v>
+        <v>1.746157747851113</v>
       </c>
       <c r="G41">
-        <v>-4.54498953171404</v>
+        <v>-5.847980529424707</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.8453565048253241</v>
       </c>
       <c r="E42">
-        <v>-24.23496849644694</v>
+        <v>-26.69021653392565</v>
       </c>
       <c r="F42">
-        <v>1.434989816663507</v>
+        <v>2.224162187432151</v>
       </c>
       <c r="G42">
-        <v>-3.80953197689171</v>
+        <v>-6.089147150869535</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.17016515524014</v>
       </c>
       <c r="E43">
-        <v>-23.87930214788451</v>
+        <v>-27.17578668787212</v>
       </c>
       <c r="F43">
-        <v>1.57016280945233</v>
+        <v>2.110329595674248</v>
       </c>
       <c r="G43">
-        <v>-4.310450622438833</v>
+        <v>-5.670747163434285</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.450339178377931</v>
       </c>
       <c r="E44">
-        <v>-23.76167050706126</v>
+        <v>-26.0183268454076</v>
       </c>
       <c r="F44">
-        <v>1.56237781260082</v>
+        <v>2.005943705777872</v>
       </c>
       <c r="G44">
-        <v>-4.484145015247774</v>
+        <v>-6.69903240284177</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.685000329817431</v>
       </c>
       <c r="E45">
-        <v>-23.30506447286786</v>
+        <v>-25.13109916087681</v>
       </c>
       <c r="F45">
-        <v>1.563143224081007</v>
+        <v>2.312451241957328</v>
       </c>
       <c r="G45">
-        <v>-4.655535268361383</v>
+        <v>-6.114529103519128</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.876857147481423</v>
       </c>
       <c r="E46">
-        <v>-21.75821020743179</v>
+        <v>-25.0681579006442</v>
       </c>
       <c r="F46">
-        <v>1.955971613836589</v>
+        <v>2.306770298308929</v>
       </c>
       <c r="G46">
-        <v>-4.419281496496835</v>
+        <v>-5.891083832346019</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.032938372231098</v>
       </c>
       <c r="E47">
-        <v>-22.42817076602257</v>
+        <v>-23.42234289271851</v>
       </c>
       <c r="F47">
-        <v>1.957504093531768</v>
+        <v>2.474748296983418</v>
       </c>
       <c r="G47">
-        <v>-4.208555341285606</v>
+        <v>-5.964971898237012</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.160356419201664</v>
       </c>
       <c r="E48">
-        <v>-20.55044807569007</v>
+        <v>-24.21523793519552</v>
       </c>
       <c r="F48">
-        <v>2.00009046170969</v>
+        <v>2.309492313594528</v>
       </c>
       <c r="G48">
-        <v>-4.928089172064041</v>
+        <v>-5.807244266563976</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.267058387512417</v>
       </c>
       <c r="E49">
-        <v>-20.1222582158948</v>
+        <v>-23.17222621632686</v>
       </c>
       <c r="F49">
-        <v>1.923716643906381</v>
+        <v>2.822649352280766</v>
       </c>
       <c r="G49">
-        <v>-4.145112046571012</v>
+        <v>-6.653307147853356</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.360310711272637</v>
       </c>
       <c r="E50">
-        <v>-18.69554436588223</v>
+        <v>-22.65911841193975</v>
       </c>
       <c r="F50">
-        <v>2.384269039045239</v>
+        <v>2.271223396319996</v>
       </c>
       <c r="G50">
-        <v>-5.205059343516086</v>
+        <v>-6.377783684801972</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.443233311678011</v>
       </c>
       <c r="E51">
-        <v>-18.12033759742794</v>
+        <v>-21.99264477833488</v>
       </c>
       <c r="F51">
-        <v>2.553946847630273</v>
+        <v>3.079507859806031</v>
       </c>
       <c r="G51">
-        <v>-5.9377757666319</v>
+        <v>-6.671309894495913</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.519709342913577</v>
       </c>
       <c r="E52">
-        <v>-18.06468718034768</v>
+        <v>-21.45106192938754</v>
       </c>
       <c r="F52">
-        <v>2.194823070759798</v>
+        <v>2.801673432907076</v>
       </c>
       <c r="G52">
-        <v>-5.860166647554765</v>
+        <v>-7.206343711825226</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.58864928159146</v>
       </c>
       <c r="E53">
-        <v>-17.7251104999345</v>
+        <v>-19.86172604928552</v>
       </c>
       <c r="F53">
-        <v>2.165909734932484</v>
+        <v>2.601804945959612</v>
       </c>
       <c r="G53">
-        <v>-5.780637412064853</v>
+        <v>-7.324692404308631</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.649376739967164</v>
       </c>
       <c r="E54">
-        <v>-16.76886887152681</v>
+        <v>-20.79493585889019</v>
       </c>
       <c r="F54">
-        <v>2.084073662475115</v>
+        <v>3.136350430986133</v>
       </c>
       <c r="G54">
-        <v>-6.302273451596736</v>
+        <v>-7.255323233078743</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.703138863274385</v>
       </c>
       <c r="E55">
-        <v>-15.67840327353178</v>
+        <v>-19.41446678544394</v>
       </c>
       <c r="F55">
-        <v>2.808300372129473</v>
+        <v>2.967212717947724</v>
       </c>
       <c r="G55">
-        <v>-6.109288509930461</v>
+        <v>-9.021638321192571</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.747370484036642</v>
       </c>
       <c r="E56">
-        <v>-15.99310957469483</v>
+        <v>-19.1562079127865</v>
       </c>
       <c r="F56">
-        <v>2.411099859221915</v>
+        <v>3.146597335758763</v>
       </c>
       <c r="G56">
-        <v>-7.225806409050601</v>
+        <v>-8.407598334568551</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.7837720676603</v>
       </c>
       <c r="E57">
-        <v>-15.3850532557889</v>
+        <v>-19.79621261581655</v>
       </c>
       <c r="F57">
-        <v>2.570857139791022</v>
+        <v>3.452551522513149</v>
       </c>
       <c r="G57">
-        <v>-7.504263015449779</v>
+        <v>-8.253350086257289</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.810985486321267</v>
       </c>
       <c r="E58">
-        <v>-15.24754614254599</v>
+        <v>-18.5387187825226</v>
       </c>
       <c r="F58">
-        <v>2.621626121173799</v>
+        <v>2.751022079695498</v>
       </c>
       <c r="G58">
-        <v>-7.238661257379591</v>
+        <v>-8.869485648207666</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.828829486244532</v>
       </c>
       <c r="E59">
-        <v>-14.94729473041542</v>
+        <v>-17.67932762771695</v>
       </c>
       <c r="F59">
-        <v>2.435427353107331</v>
+        <v>2.826097017411217</v>
       </c>
       <c r="G59">
-        <v>-7.599811980804224</v>
+        <v>-8.567471199751035</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.838104332619292</v>
       </c>
       <c r="E60">
-        <v>-13.29115933022625</v>
+        <v>-17.3500351117752</v>
       </c>
       <c r="F60">
-        <v>2.307439619170391</v>
+        <v>2.980990124591086</v>
       </c>
       <c r="G60">
-        <v>-8.199163076870498</v>
+        <v>-9.122600028503724</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.834521903130294</v>
       </c>
       <c r="E61">
-        <v>-13.79432713416652</v>
+        <v>-17.16462580047915</v>
       </c>
       <c r="F61">
-        <v>2.548042244783118</v>
+        <v>2.897437674875116</v>
       </c>
       <c r="G61">
-        <v>-8.351302507673244</v>
+        <v>-9.111387210762212</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.817589697083684</v>
       </c>
       <c r="E62">
-        <v>-13.48290850513303</v>
+        <v>-15.85820180553232</v>
       </c>
       <c r="F62">
-        <v>2.388215381352176</v>
+        <v>2.457559673375328</v>
       </c>
       <c r="G62">
-        <v>-9.234334250999666</v>
+        <v>-9.250595650688565</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.782897593350751</v>
       </c>
       <c r="E63">
-        <v>-14.64572100387461</v>
+        <v>-15.34775674386172</v>
       </c>
       <c r="F63">
-        <v>2.402083908409845</v>
+        <v>2.87273741565844</v>
       </c>
       <c r="G63">
-        <v>-8.67687148764179</v>
+        <v>-9.850757830411961</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.726680990769613</v>
       </c>
       <c r="E64">
-        <v>-12.48630458789498</v>
+        <v>-16.23965328509442</v>
       </c>
       <c r="F64">
-        <v>2.067665360960463</v>
+        <v>2.505667938660312</v>
       </c>
       <c r="G64">
-        <v>-9.751861903517312</v>
+        <v>-9.854816559243107</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.649109615544934</v>
       </c>
       <c r="E65">
-        <v>-12.597311071245</v>
+        <v>-15.95315484852515</v>
       </c>
       <c r="F65">
-        <v>2.101229151387093</v>
+        <v>2.572654697055097</v>
       </c>
       <c r="G65">
-        <v>-9.475785579360871</v>
+        <v>-9.847301620868961</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.549088184246858</v>
       </c>
       <c r="E66">
-        <v>-11.26036968996048</v>
+        <v>-15.54840437019358</v>
       </c>
       <c r="F66">
-        <v>1.980497915898676</v>
+        <v>2.103049902938446</v>
       </c>
       <c r="G66">
-        <v>-8.808353114279486</v>
+        <v>-10.4096673021705</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.430956916039904</v>
       </c>
       <c r="E67">
-        <v>-11.8438590373748</v>
+        <v>-15.6949503175558</v>
       </c>
       <c r="F67">
-        <v>1.901925611008338</v>
+        <v>2.229034644495417</v>
       </c>
       <c r="G67">
-        <v>-9.150815808134933</v>
+        <v>-9.271895700688237</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.297481429642172</v>
       </c>
       <c r="E68">
-        <v>-12.46114438630836</v>
+        <v>-14.62902452020833</v>
       </c>
       <c r="F68">
-        <v>1.964608172378176</v>
+        <v>2.431186112004998</v>
       </c>
       <c r="G68">
-        <v>-9.345664586939817</v>
+        <v>-10.5502959661332</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.151134496000988</v>
       </c>
       <c r="E69">
-        <v>-11.53976295081172</v>
+        <v>-15.78552885465723</v>
       </c>
       <c r="F69">
-        <v>1.190121098926362</v>
+        <v>2.243378654442294</v>
       </c>
       <c r="G69">
-        <v>-9.656955183997486</v>
+        <v>-10.97874676982567</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.994744997934428</v>
       </c>
       <c r="E70">
-        <v>-11.9664221863924</v>
+        <v>-14.29153546631269</v>
       </c>
       <c r="F70">
-        <v>1.675406887978007</v>
+        <v>2.327974847085791</v>
       </c>
       <c r="G70">
-        <v>-9.840680529790419</v>
+        <v>-9.67860946236986</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.825770182570085</v>
       </c>
       <c r="E71">
-        <v>-12.2921417363421</v>
+        <v>-15.36976965601301</v>
       </c>
       <c r="F71">
-        <v>1.510198949898479</v>
+        <v>1.782735138889128</v>
       </c>
       <c r="G71">
-        <v>-9.797868554876564</v>
+        <v>-9.645467590976216</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.641184230388681</v>
       </c>
       <c r="E72">
-        <v>-12.15974727025385</v>
+        <v>-15.50274376677424</v>
       </c>
       <c r="F72">
-        <v>1.376813573964897</v>
+        <v>1.915157951900657</v>
       </c>
       <c r="G72">
-        <v>-10.14863740749004</v>
+        <v>-10.0102731566762</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.435854489957241</v>
       </c>
       <c r="E73">
-        <v>-11.43659525596897</v>
+        <v>-15.70105017204414</v>
       </c>
       <c r="F73">
-        <v>1.326573090985107</v>
+        <v>1.58823612944661</v>
       </c>
       <c r="G73">
-        <v>-9.041686984978396</v>
+        <v>-10.34785279586123</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.205265549575508</v>
       </c>
       <c r="E74">
-        <v>-11.85518927934199</v>
+        <v>-15.99412395287255</v>
       </c>
       <c r="F74">
-        <v>1.142147029160631</v>
+        <v>1.459895510996077</v>
       </c>
       <c r="G74">
-        <v>-9.953033824302205</v>
+        <v>-9.047950537138698</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.9477005489179204</v>
       </c>
       <c r="E75">
-        <v>-12.48472867894031</v>
+        <v>-15.61683414092349</v>
       </c>
       <c r="F75">
-        <v>1.252309953324132</v>
+        <v>2.170734146686388</v>
       </c>
       <c r="G75">
-        <v>-8.498631715807429</v>
+        <v>-9.53956323917493</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.6634154166878821</v>
       </c>
       <c r="E76">
-        <v>-11.9010083793516</v>
+        <v>-16.0497698414788</v>
       </c>
       <c r="F76">
-        <v>1.138215597466945</v>
+        <v>1.644956102251097</v>
       </c>
       <c r="G76">
-        <v>-9.0236809277903</v>
+        <v>-9.788205072447431</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.3562950987365202</v>
       </c>
       <c r="E77">
-        <v>-13.05867653162047</v>
+        <v>-16.96037350883719</v>
       </c>
       <c r="F77">
-        <v>0.9378683141606617</v>
+        <v>1.413551668279055</v>
       </c>
       <c r="G77">
-        <v>-8.988516313072163</v>
+        <v>-8.9967893663748</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.03252953962794195</v>
       </c>
       <c r="E78">
-        <v>-13.36225637214667</v>
+        <v>-15.51212223644413</v>
       </c>
       <c r="F78">
-        <v>0.7691961436026263</v>
+        <v>1.146999605406231</v>
       </c>
       <c r="G78">
-        <v>-8.643143649687696</v>
+        <v>-9.095062910708066</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.2993793826965809</v>
       </c>
       <c r="E79">
-        <v>-14.41373633740968</v>
+        <v>-16.15415569582961</v>
       </c>
       <c r="F79">
-        <v>1.057860645925781</v>
+        <v>1.295749539926938</v>
       </c>
       <c r="G79">
-        <v>-7.293689145333357</v>
+        <v>-9.000053564276522</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.6301094071415844</v>
       </c>
       <c r="E80">
-        <v>-14.13287585097995</v>
+        <v>-16.64275992736121</v>
       </c>
       <c r="F80">
-        <v>0.1475296020888758</v>
+        <v>1.193031981979799</v>
       </c>
       <c r="G80">
-        <v>-7.91974972281047</v>
+        <v>-8.053628184418598</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.9495525953522922</v>
       </c>
       <c r="E81">
-        <v>-15.02453238309024</v>
+        <v>-17.22902522934223</v>
       </c>
       <c r="F81">
-        <v>0.7878542909832824</v>
+        <v>1.300184619001526</v>
       </c>
       <c r="G81">
-        <v>-7.512830707305413</v>
+        <v>-8.557566047497536</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.250826422255049</v>
       </c>
       <c r="E82">
-        <v>-14.97106921895569</v>
+        <v>-18.44836666912156</v>
       </c>
       <c r="F82">
-        <v>0.7702233191820977</v>
+        <v>0.7161607490057909</v>
       </c>
       <c r="G82">
-        <v>-7.411167164339933</v>
+        <v>-7.876126664239494</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.53074037818488</v>
       </c>
       <c r="E83">
-        <v>-15.83010715278873</v>
+        <v>-18.82359149692311</v>
       </c>
       <c r="F83">
-        <v>0.5539432172503692</v>
+        <v>0.994102863667109</v>
       </c>
       <c r="G83">
-        <v>-6.829626803274939</v>
+        <v>-6.836681575819126</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.789181230056749</v>
       </c>
       <c r="E84">
-        <v>-16.57262292193041</v>
+        <v>-19.48308222360816</v>
       </c>
       <c r="F84">
-        <v>0.6999744499550885</v>
+        <v>0.7371648328711751</v>
       </c>
       <c r="G84">
-        <v>-6.968868348656685</v>
+        <v>-6.808889546016944</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.032829956798838</v>
       </c>
       <c r="E85">
-        <v>-17.49096575136791</v>
+        <v>-20.3276516829867</v>
       </c>
       <c r="F85">
-        <v>0.44406773657564</v>
+        <v>0.9737681006631866</v>
       </c>
       <c r="G85">
-        <v>-6.67164094904984</v>
+        <v>-6.507080351383747</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.268551036723973</v>
       </c>
       <c r="E86">
-        <v>-19.36058247322667</v>
+        <v>-21.22034070717075</v>
       </c>
       <c r="F86">
-        <v>-0.08682133473492394</v>
+        <v>0.5283218134817805</v>
       </c>
       <c r="G86">
-        <v>-5.945138419911238</v>
+        <v>-5.945442990100852</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.505368861010066</v>
       </c>
       <c r="E87">
-        <v>-19.86975050522711</v>
+        <v>-21.81868797780423</v>
       </c>
       <c r="F87">
-        <v>0.3170516776021834</v>
+        <v>0.3626764974135746</v>
       </c>
       <c r="G87">
-        <v>-5.419192050087225</v>
+        <v>-6.554149687861106</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.749448511925423</v>
       </c>
       <c r="E88">
-        <v>-19.92099924557191</v>
+        <v>-22.86535417519708</v>
       </c>
       <c r="F88">
-        <v>0.3070019242714198</v>
+        <v>0.1089798682647952</v>
       </c>
       <c r="G88">
-        <v>-5.649940384719966</v>
+        <v>-5.61035950225244</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.000869070575619</v>
       </c>
       <c r="E89">
-        <v>-22.05037376498466</v>
+        <v>-24.41521081890023</v>
       </c>
       <c r="F89">
-        <v>-0.2022361082321734</v>
+        <v>-0.03034821541647044</v>
       </c>
       <c r="G89">
-        <v>-6.107603442250972</v>
+        <v>-5.851334112055989</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.259446301852863</v>
       </c>
       <c r="E90">
-        <v>-23.72652954876174</v>
+        <v>-26.03966048645774</v>
       </c>
       <c r="F90">
-        <v>0.0262127108466798</v>
+        <v>-0.09775495608447461</v>
       </c>
       <c r="G90">
-        <v>-5.392177998486772</v>
+        <v>-6.016821662473077</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.515913260959099</v>
       </c>
       <c r="E91">
-        <v>-25.5176768730156</v>
+        <v>-26.20029904493183</v>
       </c>
       <c r="F91">
-        <v>-0.4417825654063317</v>
+        <v>-0.4946829361165109</v>
       </c>
       <c r="G91">
-        <v>-5.256061608094098</v>
+        <v>-6.305557512771693</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.759116698485745</v>
       </c>
       <c r="E92">
-        <v>-26.36725935312063</v>
+        <v>-28.66463120126993</v>
       </c>
       <c r="F92">
-        <v>-0.2161866436627199</v>
+        <v>-0.4260170769962515</v>
       </c>
       <c r="G92">
-        <v>-4.733273498714549</v>
+        <v>-6.137646643019858</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>3.974580261405043</v>
       </c>
       <c r="E93">
-        <v>-27.93868964699632</v>
+        <v>-30.68066028050769</v>
       </c>
       <c r="F93">
-        <v>-0.9988497033801657</v>
+        <v>-1.170461749850736</v>
       </c>
       <c r="G93">
-        <v>-4.941516744771325</v>
+        <v>-5.867883529206806</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.142699995666688</v>
       </c>
       <c r="E94">
-        <v>-30.48869600308554</v>
+        <v>-31.56049523122096</v>
       </c>
       <c r="F94">
-        <v>-0.8938417095642863</v>
+        <v>-0.8716754262327743</v>
       </c>
       <c r="G94">
-        <v>-4.870210904400962</v>
+        <v>-5.947886172708833</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.251335829797717</v>
       </c>
       <c r="E95">
-        <v>-32.27581977818358</v>
+        <v>-33.35365772640823</v>
       </c>
       <c r="F95">
-        <v>-1.221292858788722</v>
+        <v>-1.004007118829995</v>
       </c>
       <c r="G95">
-        <v>-5.380329556001721</v>
+        <v>-6.15844017955202</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.27795396961477</v>
       </c>
       <c r="E96">
-        <v>-34.82493176065628</v>
+        <v>-36.70790068812667</v>
       </c>
       <c r="F96">
-        <v>-1.344123177275833</v>
+        <v>-1.690652456154145</v>
       </c>
       <c r="G96">
-        <v>-5.120855617724724</v>
+        <v>-5.403198804587006</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>4.219907329684534</v>
       </c>
       <c r="E97">
-        <v>-36.33379892187902</v>
+        <v>-38.56498938664322</v>
       </c>
       <c r="F97">
-        <v>-1.779091445179228</v>
+        <v>-1.973435549917423</v>
       </c>
       <c r="G97">
-        <v>-6.193955712097321</v>
+        <v>-6.355189211496446</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>4.052456105422808</v>
       </c>
       <c r="E98">
-        <v>-38.64581585496912</v>
+        <v>-40.15518794104371</v>
       </c>
       <c r="F98">
-        <v>-2.182121179500286</v>
+        <v>-1.786300726685792</v>
       </c>
       <c r="G98">
-        <v>-5.886389478771332</v>
+        <v>-6.728824002149671</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>3.794794549012652</v>
       </c>
       <c r="E99">
-        <v>-41.95291966650471</v>
+        <v>-41.72118180187319</v>
       </c>
       <c r="F99">
-        <v>-1.970530465435805</v>
+        <v>-2.631733326350371</v>
       </c>
       <c r="G99">
-        <v>-5.733316474126511</v>
+        <v>-6.976790484132161</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>3.407616838033126</v>
       </c>
       <c r="E100">
-        <v>-42.78561320279814</v>
+        <v>-44.49087122478551</v>
       </c>
       <c r="F100">
-        <v>-2.781980120767936</v>
+        <v>-2.775846060150206</v>
       </c>
       <c r="G100">
-        <v>-6.465304577223685</v>
+        <v>-7.364839390063373</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>2.960091360888037</v>
       </c>
       <c r="E101">
-        <v>-44.4271012538095</v>
+        <v>-46.00672355716507</v>
       </c>
       <c r="F101">
-        <v>-2.526027018813931</v>
+        <v>-3.242335364464928</v>
       </c>
       <c r="G101">
-        <v>-6.323643023052731</v>
+        <v>-6.787284925827661</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.344688612791904</v>
       </c>
       <c r="E102">
-        <v>-48.09531916813875</v>
+        <v>-48.07746565936351</v>
       </c>
       <c r="F102">
-        <v>-2.75626759658504</v>
+        <v>-3.131304311263294</v>
       </c>
       <c r="G102">
-        <v>-7.09290124783102</v>
+        <v>-7.346978996879005</v>
       </c>
     </row>
   </sheetData>
